--- a/review/review_UG_20261012.xlsx
+++ b/review/review_UG_20261012.xlsx
@@ -11,7 +11,7 @@
     <sheet name="review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'review'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'review'!$A$1:$P$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -598,10 +598,12 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,20 +659,30 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
+          <t>コアカリ</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>出題基準</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>Claude Codeによる修正</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>修正案</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>コメント</t>
         </is>
@@ -725,9 +737,11 @@
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -773,9 +787,11 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -826,9 +842,11 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -874,9 +892,11 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -918,9 +938,11 @@
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -967,9 +989,11 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1015,9 +1039,11 @@
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1067,9 +1093,11 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1112,9 +1140,11 @@
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1160,9 +1190,11 @@
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1204,9 +1236,11 @@
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1248,9 +1282,11 @@
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1297,9 +1333,11 @@
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1345,9 +1383,11 @@
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1393,9 +1433,11 @@
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1446,9 +1488,11 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1494,9 +1538,11 @@
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1538,14 +1584,16 @@
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N19"/>
+  <autoFilter ref="A1:P19"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,修正,削除"</formula1>
     </dataValidation>
   </dataValidations>
